--- a/documentation/3_1_Modele_Journal.xlsx
+++ b/documentation/3_1_Modele_Journal.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
   <workbookPr checkCompatibility="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\stu.net.fr.ch\perso$\Users\BersierN04\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduetatfr-my.sharepoint.com/personal/emma_morales_studentfr_ch/Documents/EMF/3ème année/bloc 3/module 306/projet-306-tercier-morales-bersier/documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DBC8D265-1C83-4238-817E-722DE2E9B57C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E5210B34-28DC-4E6C-B2E0-2882AAE563C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal_BERSIER_NOE" sheetId="8" r:id="rId1"/>
@@ -21,12 +21,12 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Journal_BERSIER_NOE!$A$5:$HI$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Journal_MORALES_EMMA!$A$5:$HI$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Journal_Tercier-_Elouan'!$A$5:$HI$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Journal_BERSIER_NOE!$A$1:$D$83</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Journal_MORALES_EMMA!$A$1:$D$83</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Journal_Tercier-_Elouan'!$A$1:$D$83</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Journal_BERSIER_NOE!$B:$D,Journal_BERSIER_NOE!$1:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">Journal_MORALES_EMMA!$B:$D,Journal_MORALES_EMMA!$1:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Journal_Tercier-_Elouan'!$B:$D,'Journal_Tercier-_Elouan'!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Journal_BERSIER_NOE!$A$1:$D$83</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">Journal_MORALES_EMMA!$A$1:$D$83</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Journal_Tercier-_Elouan'!$A$1:$D$83</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="94">
   <si>
     <r>
       <t>Projet :</t>
@@ -378,6 +378,42 @@
   </si>
   <si>
     <t xml:space="preserve">Je trouve que j'ai bien avancé, j'ai même pu commencer une tâche de la V3. </t>
+  </si>
+  <si>
+    <t>12.01.26</t>
+  </si>
+  <si>
+    <t>configuration raspéry pi avec les script + test avec interface</t>
+  </si>
+  <si>
+    <t>débugage</t>
+  </si>
+  <si>
+    <t>création de la démo</t>
+  </si>
+  <si>
+    <t>tout c'est bien passé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je fini l'interface utilisateur avec le tableau de présence + salaire </t>
+  </si>
+  <si>
+    <t>Finir l'interface admin avec le tableau de présence, correction de bug</t>
+  </si>
+  <si>
+    <t>Réalisation de la documentation + début de la présentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je trouve que j'ai bien avancé, j'ai fini tout ce que je voulais à temps. </t>
+  </si>
+  <si>
+    <t>WebSummary</t>
+  </si>
+  <si>
+    <t>Présentation</t>
+  </si>
+  <si>
+    <t>J'ai eu pas mal à faire avec la documentation aujourd'hui mais j'ai beaucoup avancé</t>
   </si>
 </sst>
 </file>
@@ -739,8 +775,16 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -748,6 +792,10 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -779,20 +827,8 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -831,13 +867,13 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="72">
     <dxf>
@@ -1998,16 +2034,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D84"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.54296875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" style="1"/>
-    <col min="2" max="3" width="31.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" style="1" customWidth="1"/>
-    <col min="5" max="217" width="9.140625" style="1" customWidth="1"/>
-    <col min="218" max="16384" width="11.5703125" style="1"/>
+    <col min="1" max="1" width="11.54296875" style="1"/>
+    <col min="2" max="3" width="31.7265625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.7265625" style="1" customWidth="1"/>
+    <col min="5" max="217" width="9.1796875" style="1" customWidth="1"/>
+    <col min="218" max="16384" width="11.54296875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="20" x14ac:dyDescent="0.4">
       <c r="A1" s="31" t="s">
         <v>16</v>
       </c>
@@ -2015,7 +2051,7 @@
       <c r="C1" s="31"/>
       <c r="D1" s="31"/>
     </row>
-    <row r="2" spans="1:4" ht="18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A2" s="38" t="s">
         <v>17</v>
       </c>
@@ -2025,7 +2061,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="32" t="s">
         <v>2</v>
       </c>
@@ -2037,7 +2073,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="34"/>
       <c r="B5" s="34"/>
       <c r="C5" s="35"/>
@@ -2045,8 +2081,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="40">
+    <row r="6" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="30">
         <v>45992</v>
       </c>
       <c r="B6" s="36" t="s">
@@ -2057,44 +2093,44 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="19"/>
-      <c r="B7" s="22" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="21"/>
+      <c r="B7" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="23"/>
+      <c r="C7" s="26"/>
       <c r="D7" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="19"/>
-      <c r="B8" s="22" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="21"/>
+      <c r="B8" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="23"/>
+      <c r="C8" s="26"/>
       <c r="D8" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="19"/>
-      <c r="B9" s="22" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="21"/>
+      <c r="B9" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="23"/>
+      <c r="C9" s="26"/>
       <c r="D9" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="19"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="23"/>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="21"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="26"/>
       <c r="D10" s="8"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="19"/>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="21"/>
       <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
@@ -2106,56 +2142,56 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="19"/>
-      <c r="B12" s="24" t="s">
+    <row r="12" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="21"/>
+      <c r="B12" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="26"/>
-    </row>
-    <row r="13" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="18">
+      <c r="C12" s="28"/>
+      <c r="D12" s="29"/>
+    </row>
+    <row r="13" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="20">
         <v>45993</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="21"/>
+      <c r="C13" s="24"/>
       <c r="D13" s="7">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="19"/>
-      <c r="B14" s="22" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="21"/>
+      <c r="B14" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="23"/>
+      <c r="C14" s="26"/>
       <c r="D14" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="19"/>
-      <c r="B15" s="22"/>
-      <c r="C15" s="23"/>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="21"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="26"/>
       <c r="D15" s="8"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="19"/>
-      <c r="B16" s="22"/>
-      <c r="C16" s="23"/>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="21"/>
+      <c r="B16" s="25"/>
+      <c r="C16" s="26"/>
       <c r="D16" s="8"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="19"/>
-      <c r="B17" s="22"/>
-      <c r="C17" s="23"/>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="21"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="26"/>
       <c r="D17" s="8"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="19"/>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="21"/>
       <c r="B18" s="2" t="s">
         <v>6</v>
       </c>
@@ -2167,54 +2203,54 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="19"/>
-      <c r="B19" s="24"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="26"/>
-    </row>
-    <row r="20" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="18">
+    <row r="19" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="21"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="29"/>
+    </row>
+    <row r="20" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="20">
         <v>46000</v>
       </c>
-      <c r="B20" s="20" t="s">
+      <c r="B20" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="21"/>
+      <c r="C20" s="24"/>
       <c r="D20" s="7">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="19"/>
-      <c r="B21" s="22" t="s">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="21"/>
+      <c r="B21" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="C21" s="23"/>
+      <c r="C21" s="26"/>
       <c r="D21" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="19"/>
-      <c r="B22" s="22"/>
-      <c r="C22" s="23"/>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="21"/>
+      <c r="B22" s="25"/>
+      <c r="C22" s="26"/>
       <c r="D22" s="8"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="19"/>
-      <c r="B23" s="22"/>
-      <c r="C23" s="23"/>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="21"/>
+      <c r="B23" s="25"/>
+      <c r="C23" s="26"/>
       <c r="D23" s="8"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="19"/>
-      <c r="B24" s="22"/>
-      <c r="C24" s="23"/>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="21"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="26"/>
       <c r="D24" s="8"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="19"/>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="21"/>
       <c r="B25" s="2" t="s">
         <v>6</v>
       </c>
@@ -2226,16 +2262,16 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="19"/>
-      <c r="B26" s="24" t="s">
+    <row r="26" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="21"/>
+      <c r="B26" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="C26" s="25"/>
-      <c r="D26" s="26"/>
-    </row>
-    <row r="27" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="18">
+      <c r="C26" s="28"/>
+      <c r="D26" s="29"/>
+    </row>
+    <row r="27" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="20">
         <v>46006</v>
       </c>
       <c r="B27" s="13" t="s">
@@ -2246,8 +2282,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="19"/>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="21"/>
       <c r="B28" s="15" t="s">
         <v>39</v>
       </c>
@@ -2256,8 +2292,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="19"/>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="21"/>
       <c r="B29" s="15" t="s">
         <v>40</v>
       </c>
@@ -2266,20 +2302,20 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="19"/>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="21"/>
       <c r="B30" s="15"/>
       <c r="C30" s="16"/>
       <c r="D30" s="8"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="19"/>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="21"/>
       <c r="B31" s="15"/>
       <c r="C31" s="16"/>
       <c r="D31" s="8"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="19"/>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="21"/>
       <c r="B32" s="2" t="s">
         <v>6</v>
       </c>
@@ -2291,56 +2327,56 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="27"/>
-      <c r="B33" s="28" t="s">
+    <row r="33" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="22"/>
+      <c r="B33" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C33" s="29"/>
-      <c r="D33" s="30"/>
-    </row>
-    <row r="34" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="18">
+      <c r="C33" s="18"/>
+      <c r="D33" s="19"/>
+    </row>
+    <row r="34" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="20">
         <v>46007</v>
       </c>
-      <c r="B34" s="20" t="s">
+      <c r="B34" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="C34" s="21"/>
+      <c r="C34" s="24"/>
       <c r="D34" s="7">
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="19"/>
-      <c r="B35" s="22" t="s">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="21"/>
+      <c r="B35" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="C35" s="23"/>
+      <c r="C35" s="26"/>
       <c r="D35" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="19"/>
-      <c r="B36" s="22"/>
-      <c r="C36" s="23"/>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="21"/>
+      <c r="B36" s="25"/>
+      <c r="C36" s="26"/>
       <c r="D36" s="8"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="19"/>
-      <c r="B37" s="22"/>
-      <c r="C37" s="23"/>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="21"/>
+      <c r="B37" s="25"/>
+      <c r="C37" s="26"/>
       <c r="D37" s="8"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="19"/>
-      <c r="B38" s="22"/>
-      <c r="C38" s="23"/>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="21"/>
+      <c r="B38" s="25"/>
+      <c r="C38" s="26"/>
       <c r="D38" s="8"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="19"/>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="21"/>
       <c r="B39" s="2" t="s">
         <v>6</v>
       </c>
@@ -2352,60 +2388,60 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="27"/>
-      <c r="B40" s="28" t="s">
+    <row r="40" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="22"/>
+      <c r="B40" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="C40" s="29"/>
-      <c r="D40" s="30"/>
-    </row>
-    <row r="41" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="18">
+      <c r="C40" s="18"/>
+      <c r="D40" s="19"/>
+    </row>
+    <row r="41" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="20">
         <v>46027</v>
       </c>
-      <c r="B41" s="20" t="s">
+      <c r="B41" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="C41" s="21"/>
+      <c r="C41" s="24"/>
       <c r="D41" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="19"/>
-      <c r="B42" s="22" t="s">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="21"/>
+      <c r="B42" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="C42" s="23"/>
+      <c r="C42" s="26"/>
       <c r="D42" s="8">
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="19"/>
-      <c r="B43" s="22" t="s">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="21"/>
+      <c r="B43" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="C43" s="23"/>
+      <c r="C43" s="26"/>
       <c r="D43" s="8">
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="19"/>
-      <c r="B44" s="22"/>
-      <c r="C44" s="23"/>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="21"/>
+      <c r="B44" s="25"/>
+      <c r="C44" s="26"/>
       <c r="D44" s="8"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="19"/>
-      <c r="B45" s="22"/>
-      <c r="C45" s="23"/>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="21"/>
+      <c r="B45" s="25"/>
+      <c r="C45" s="26"/>
       <c r="D45" s="8"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="19"/>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="21"/>
       <c r="B46" s="2" t="s">
         <v>6</v>
       </c>
@@ -2417,56 +2453,56 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="27"/>
-      <c r="B47" s="28" t="s">
+    <row r="47" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="22"/>
+      <c r="B47" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="C47" s="29"/>
-      <c r="D47" s="30"/>
-    </row>
-    <row r="48" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="18">
+      <c r="C47" s="18"/>
+      <c r="D47" s="19"/>
+    </row>
+    <row r="48" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="20">
         <v>46028</v>
       </c>
-      <c r="B48" s="20" t="s">
+      <c r="B48" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="C48" s="21"/>
+      <c r="C48" s="24"/>
       <c r="D48" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="19"/>
-      <c r="B49" s="22" t="s">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="21"/>
+      <c r="B49" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="C49" s="23"/>
+      <c r="C49" s="26"/>
       <c r="D49" s="8">
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="19"/>
-      <c r="B50" s="22"/>
-      <c r="C50" s="23"/>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="21"/>
+      <c r="B50" s="25"/>
+      <c r="C50" s="26"/>
       <c r="D50" s="8"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="19"/>
-      <c r="B51" s="22"/>
-      <c r="C51" s="23"/>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="21"/>
+      <c r="B51" s="25"/>
+      <c r="C51" s="26"/>
       <c r="D51" s="8"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A52" s="19"/>
-      <c r="B52" s="22"/>
-      <c r="C52" s="23"/>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="21"/>
+      <c r="B52" s="25"/>
+      <c r="C52" s="26"/>
       <c r="D52" s="8"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="19"/>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="21"/>
       <c r="B53" s="2" t="s">
         <v>6</v>
       </c>
@@ -2478,48 +2514,60 @@
         <v>4</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="27"/>
-      <c r="B54" s="28" t="s">
+    <row r="54" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="22"/>
+      <c r="B54" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="C54" s="29"/>
-      <c r="D54" s="30"/>
-    </row>
-    <row r="55" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="18">
+      <c r="C54" s="18"/>
+      <c r="D54" s="19"/>
+    </row>
+    <row r="55" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="20">
         <v>46034</v>
       </c>
-      <c r="B55" s="20"/>
-      <c r="C55" s="21"/>
-      <c r="D55" s="7"/>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="19"/>
-      <c r="B56" s="22"/>
-      <c r="C56" s="23"/>
-      <c r="D56" s="8"/>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="19"/>
-      <c r="B57" s="22"/>
-      <c r="C57" s="23"/>
-      <c r="D57" s="8"/>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A58" s="19"/>
-      <c r="B58" s="22"/>
-      <c r="C58" s="23"/>
+      <c r="B55" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="C55" s="24"/>
+      <c r="D55" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="21"/>
+      <c r="B56" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="C56" s="26"/>
+      <c r="D56" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="21"/>
+      <c r="B57" s="25" t="s">
+        <v>92</v>
+      </c>
+      <c r="C57" s="26"/>
+      <c r="D57" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="21"/>
+      <c r="B58" s="25"/>
+      <c r="C58" s="26"/>
       <c r="D58" s="8"/>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A59" s="19"/>
-      <c r="B59" s="22"/>
-      <c r="C59" s="23"/>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="21"/>
+      <c r="B59" s="25"/>
+      <c r="C59" s="26"/>
       <c r="D59" s="8"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" s="19"/>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="21"/>
       <c r="B60" s="2" t="s">
         <v>6</v>
       </c>
@@ -2528,49 +2576,51 @@
       </c>
       <c r="D60" s="9">
         <f>SUM(D55:D59)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="27"/>
-      <c r="B61" s="28"/>
-      <c r="C61" s="29"/>
-      <c r="D61" s="30"/>
-    </row>
-    <row r="62" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="22"/>
+      <c r="B61" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="C61" s="18"/>
+      <c r="D61" s="19"/>
+    </row>
+    <row r="62" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="20">
         <v>46035</v>
       </c>
-      <c r="B62" s="20"/>
-      <c r="C62" s="21"/>
+      <c r="B62" s="23"/>
+      <c r="C62" s="24"/>
       <c r="D62" s="7"/>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A63" s="19"/>
-      <c r="B63" s="22"/>
-      <c r="C63" s="23"/>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="21"/>
+      <c r="B63" s="25"/>
+      <c r="C63" s="26"/>
       <c r="D63" s="8"/>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A64" s="19"/>
-      <c r="B64" s="22"/>
-      <c r="C64" s="23"/>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="21"/>
+      <c r="B64" s="25"/>
+      <c r="C64" s="26"/>
       <c r="D64" s="8"/>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A65" s="19"/>
-      <c r="B65" s="22"/>
-      <c r="C65" s="23"/>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="21"/>
+      <c r="B65" s="25"/>
+      <c r="C65" s="26"/>
       <c r="D65" s="8"/>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A66" s="19"/>
-      <c r="B66" s="22"/>
-      <c r="C66" s="23"/>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="21"/>
+      <c r="B66" s="25"/>
+      <c r="C66" s="26"/>
       <c r="D66" s="8"/>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A67" s="19"/>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="21"/>
       <c r="B67" s="2" t="s">
         <v>6</v>
       </c>
@@ -2582,44 +2632,44 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="19"/>
-      <c r="B68" s="24"/>
-      <c r="C68" s="25"/>
-      <c r="D68" s="26"/>
-    </row>
-    <row r="69" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="18"/>
-      <c r="B69" s="20"/>
-      <c r="C69" s="21"/>
+    <row r="68" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="21"/>
+      <c r="B68" s="27"/>
+      <c r="C68" s="28"/>
+      <c r="D68" s="29"/>
+    </row>
+    <row r="69" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="20"/>
+      <c r="B69" s="23"/>
+      <c r="C69" s="24"/>
       <c r="D69" s="7"/>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A70" s="19"/>
-      <c r="B70" s="22"/>
-      <c r="C70" s="23"/>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="21"/>
+      <c r="B70" s="25"/>
+      <c r="C70" s="26"/>
       <c r="D70" s="8"/>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A71" s="19"/>
-      <c r="B71" s="22"/>
-      <c r="C71" s="23"/>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="21"/>
+      <c r="B71" s="25"/>
+      <c r="C71" s="26"/>
       <c r="D71" s="8"/>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A72" s="19"/>
-      <c r="B72" s="22"/>
-      <c r="C72" s="23"/>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="21"/>
+      <c r="B72" s="25"/>
+      <c r="C72" s="26"/>
       <c r="D72" s="8"/>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A73" s="19"/>
-      <c r="B73" s="22"/>
-      <c r="C73" s="23"/>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="21"/>
+      <c r="B73" s="25"/>
+      <c r="C73" s="26"/>
       <c r="D73" s="8"/>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A74" s="19"/>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="21"/>
       <c r="B74" s="2" t="s">
         <v>6</v>
       </c>
@@ -2631,44 +2681,44 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="27"/>
-      <c r="B75" s="28"/>
-      <c r="C75" s="29"/>
-      <c r="D75" s="30"/>
-    </row>
-    <row r="76" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="18"/>
-      <c r="B76" s="20"/>
-      <c r="C76" s="21"/>
+    <row r="75" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="22"/>
+      <c r="B75" s="17"/>
+      <c r="C75" s="18"/>
+      <c r="D75" s="19"/>
+    </row>
+    <row r="76" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="20"/>
+      <c r="B76" s="23"/>
+      <c r="C76" s="24"/>
       <c r="D76" s="7"/>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A77" s="19"/>
-      <c r="B77" s="22"/>
-      <c r="C77" s="23"/>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="21"/>
+      <c r="B77" s="25"/>
+      <c r="C77" s="26"/>
       <c r="D77" s="8"/>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A78" s="19"/>
-      <c r="B78" s="22"/>
-      <c r="C78" s="23"/>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="21"/>
+      <c r="B78" s="25"/>
+      <c r="C78" s="26"/>
       <c r="D78" s="8"/>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A79" s="19"/>
-      <c r="B79" s="22"/>
-      <c r="C79" s="23"/>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="21"/>
+      <c r="B79" s="25"/>
+      <c r="C79" s="26"/>
       <c r="D79" s="8"/>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A80" s="19"/>
-      <c r="B80" s="22"/>
-      <c r="C80" s="23"/>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="21"/>
+      <c r="B80" s="25"/>
+      <c r="C80" s="26"/>
       <c r="D80" s="8"/>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A81" s="19"/>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="21"/>
       <c r="B81" s="2" t="s">
         <v>6</v>
       </c>
@@ -2680,13 +2730,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="27"/>
-      <c r="B82" s="28"/>
-      <c r="C82" s="29"/>
-      <c r="D82" s="30"/>
-    </row>
-    <row r="83" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="22"/>
+      <c r="B82" s="17"/>
+      <c r="C82" s="18"/>
+      <c r="D82" s="19"/>
+    </row>
+    <row r="83" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="11"/>
       <c r="B83" s="10"/>
       <c r="C83" s="3" t="s">
@@ -2694,53 +2744,46 @@
       </c>
       <c r="D83" s="12">
         <f>D11+D18+D25+D32+D39+'Journal_Tercier-_Elouan'!D46+'Journal_Tercier-_Elouan'!D53+D60+D67+D74+D81</f>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A84" s="17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="B84" s="17"/>
-      <c r="C84" s="17"/>
-      <c r="D84" s="17"/>
+      <c r="B84" s="40"/>
+      <c r="C84" s="40"/>
+      <c r="D84" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="77">
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="A48:A54"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="A20:A26"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="A76:A82"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="A69:A75"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B75:D75"/>
+    <mergeCell ref="A84:D84"/>
+    <mergeCell ref="A13:A19"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A27:A33"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="A34:A40"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B4:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="A6:A12"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B12:D12"/>
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="A62:A68"/>
     <mergeCell ref="B62:C62"/>
@@ -2757,33 +2800,40 @@
     <mergeCell ref="B59:C59"/>
     <mergeCell ref="B61:D61"/>
     <mergeCell ref="A41:A47"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="A6:A12"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B4:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A84:D84"/>
-    <mergeCell ref="A13:A19"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A27:A33"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="A34:A40"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="A69:A75"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B75:D75"/>
+    <mergeCell ref="A76:A82"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="A20:A26"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="A48:A54"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B54:D54"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D11">
     <cfRule type="containsText" dxfId="71" priority="27" operator="containsText" text="Terminé">
@@ -2825,60 +2875,60 @@
       <formula>NOT(ISERROR(SEARCH("En cours",D34)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D41:D46">
+    <cfRule type="containsText" dxfId="61" priority="3" operator="containsText" text="Terminé">
+      <formula>NOT(ISERROR(SEARCH("Terminé",D41)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="60" priority="4" operator="containsText" text="En cours">
+      <formula>NOT(ISERROR(SEARCH("En cours",D41)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D48:D53">
+    <cfRule type="containsText" dxfId="59" priority="1" operator="containsText" text="Terminé">
+      <formula>NOT(ISERROR(SEARCH("Terminé",D48)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="58" priority="2" operator="containsText" text="En cours">
+      <formula>NOT(ISERROR(SEARCH("En cours",D48)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="D55:D60">
-    <cfRule type="containsText" dxfId="61" priority="9" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="57" priority="9" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D55)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="60" priority="10" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="56" priority="10" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D55)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D62:D67">
-    <cfRule type="containsText" dxfId="59" priority="19" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="55" priority="19" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D62)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="58" priority="20" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="54" priority="20" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D62)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D69:D74">
-    <cfRule type="containsText" dxfId="57" priority="17" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="53" priority="17" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D69)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="56" priority="18" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="52" priority="18" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D69)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D76:D81">
-    <cfRule type="containsText" dxfId="55" priority="15" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="51" priority="15" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D76)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="54" priority="16" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="50" priority="16" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D76)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D83">
-    <cfRule type="containsText" dxfId="53" priority="5" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="49" priority="5" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D83)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="52" priority="6" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="48" priority="6" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D83)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D41:D46">
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D41)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D41)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D48:D53">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D48)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D48)))</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
@@ -2900,16 +2950,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{971094A1-2086-4124-85CF-EAAE0115819F}">
   <dimension ref="A1:D84"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.54296875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" style="1"/>
-    <col min="2" max="3" width="31.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" style="1" customWidth="1"/>
-    <col min="5" max="217" width="9.140625" style="1" customWidth="1"/>
-    <col min="218" max="16384" width="11.5703125" style="1"/>
+    <col min="1" max="1" width="11.54296875" style="1"/>
+    <col min="2" max="3" width="31.7265625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.7265625" style="1" customWidth="1"/>
+    <col min="5" max="217" width="9.1796875" style="1" customWidth="1"/>
+    <col min="218" max="16384" width="11.54296875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="20" x14ac:dyDescent="0.4">
       <c r="A1" s="31" t="s">
         <v>10</v>
       </c>
@@ -2917,7 +2967,7 @@
       <c r="C1" s="31"/>
       <c r="D1" s="31"/>
     </row>
-    <row r="2" spans="1:4" ht="18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A2" s="38" t="s">
         <v>11</v>
       </c>
@@ -2927,7 +2977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="32" t="s">
         <v>2</v>
       </c>
@@ -2939,7 +2989,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="34"/>
       <c r="B5" s="34"/>
       <c r="C5" s="35"/>
@@ -2947,8 +2997,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="40">
+    <row r="6" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="30">
         <v>45992</v>
       </c>
       <c r="B6" s="36" t="s">
@@ -2959,34 +3009,34 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="19"/>
-      <c r="B7" s="22" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="21"/>
+      <c r="B7" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="23"/>
+      <c r="C7" s="26"/>
       <c r="D7" s="8">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="19"/>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="21"/>
       <c r="D8" s="8"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="19"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="23"/>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="21"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="26"/>
       <c r="D9" s="8"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="19"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="23"/>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="21"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="26"/>
       <c r="D10" s="8"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="19"/>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="21"/>
       <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
@@ -2998,54 +3048,54 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="19"/>
-      <c r="B12" s="24"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="26"/>
-    </row>
-    <row r="13" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="18">
+    <row r="12" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="21"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="29"/>
+    </row>
+    <row r="13" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="20">
         <v>45993</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="21"/>
+      <c r="C13" s="24"/>
       <c r="D13" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="19"/>
-      <c r="B14" s="22" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="21"/>
+      <c r="B14" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="23"/>
+      <c r="C14" s="26"/>
       <c r="D14" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="19"/>
-      <c r="B15" s="22"/>
-      <c r="C15" s="23"/>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="21"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="26"/>
       <c r="D15" s="8"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="19"/>
-      <c r="B16" s="22"/>
-      <c r="C16" s="23"/>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="21"/>
+      <c r="B16" s="25"/>
+      <c r="C16" s="26"/>
       <c r="D16" s="8"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="19"/>
-      <c r="B17" s="22"/>
-      <c r="C17" s="23"/>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="21"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="26"/>
       <c r="D17" s="8"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="19"/>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="21"/>
       <c r="B18" s="2" t="s">
         <v>6</v>
       </c>
@@ -3057,62 +3107,62 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="19"/>
-      <c r="B19" s="24"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="26"/>
-    </row>
-    <row r="20" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="18">
+    <row r="19" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="21"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="29"/>
+    </row>
+    <row r="20" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="20">
         <v>46000</v>
       </c>
-      <c r="B20" s="20" t="s">
+      <c r="B20" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="21"/>
+      <c r="C20" s="24"/>
       <c r="D20" s="7">
         <v>0.5</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="19"/>
-      <c r="B21" s="22" t="s">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="21"/>
+      <c r="B21" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="23"/>
+      <c r="C21" s="26"/>
       <c r="D21" s="8">
         <v>0.5</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="19"/>
-      <c r="B22" s="22" t="s">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="21"/>
+      <c r="B22" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="23"/>
+      <c r="C22" s="26"/>
       <c r="D22" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="19"/>
-      <c r="B23" s="22" t="s">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="21"/>
+      <c r="B23" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C23" s="23"/>
+      <c r="C23" s="26"/>
       <c r="D23" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="19"/>
-      <c r="B24" s="22"/>
-      <c r="C24" s="23"/>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="21"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="26"/>
       <c r="D24" s="8"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="19"/>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="21"/>
       <c r="B25" s="2" t="s">
         <v>6</v>
       </c>
@@ -3124,58 +3174,58 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="19"/>
-      <c r="B26" s="24"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="26"/>
-    </row>
-    <row r="27" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="18">
+    <row r="26" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="21"/>
+      <c r="B26" s="27"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="29"/>
+    </row>
+    <row r="27" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="20">
         <v>46006</v>
       </c>
-      <c r="B27" s="20" t="s">
+      <c r="B27" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="C27" s="21"/>
+      <c r="C27" s="24"/>
       <c r="D27" s="7">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="19"/>
-      <c r="B28" s="22" t="s">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="21"/>
+      <c r="B28" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="C28" s="23"/>
+      <c r="C28" s="26"/>
       <c r="D28" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="19"/>
-      <c r="B29" s="22" t="s">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="21"/>
+      <c r="B29" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="C29" s="23"/>
+      <c r="C29" s="26"/>
       <c r="D29" s="8">
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="19"/>
-      <c r="B30" s="22"/>
-      <c r="C30" s="23"/>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="21"/>
+      <c r="B30" s="25"/>
+      <c r="C30" s="26"/>
       <c r="D30" s="8"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="19"/>
-      <c r="B31" s="22"/>
-      <c r="C31" s="23"/>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="21"/>
+      <c r="B31" s="25"/>
+      <c r="C31" s="26"/>
       <c r="D31" s="8"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="19"/>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="21"/>
       <c r="B32" s="2" t="s">
         <v>6</v>
       </c>
@@ -3187,56 +3237,56 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="27"/>
-      <c r="B33" s="28" t="s">
+    <row r="33" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="22"/>
+      <c r="B33" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="C33" s="29"/>
-      <c r="D33" s="30"/>
-    </row>
-    <row r="34" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="18">
+      <c r="C33" s="18"/>
+      <c r="D33" s="19"/>
+    </row>
+    <row r="34" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="20">
         <v>46007</v>
       </c>
-      <c r="B34" s="20" t="s">
+      <c r="B34" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="C34" s="21"/>
+      <c r="C34" s="24"/>
       <c r="D34" s="7">
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="19"/>
-      <c r="B35" s="22" t="s">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="21"/>
+      <c r="B35" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="C35" s="23"/>
+      <c r="C35" s="26"/>
       <c r="D35" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="19"/>
-      <c r="B36" s="22"/>
-      <c r="C36" s="23"/>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="21"/>
+      <c r="B36" s="25"/>
+      <c r="C36" s="26"/>
       <c r="D36" s="8"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="19"/>
-      <c r="B37" s="22"/>
-      <c r="C37" s="23"/>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="21"/>
+      <c r="B37" s="25"/>
+      <c r="C37" s="26"/>
       <c r="D37" s="8"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="19"/>
-      <c r="B38" s="22"/>
-      <c r="C38" s="23"/>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="21"/>
+      <c r="B38" s="25"/>
+      <c r="C38" s="26"/>
       <c r="D38" s="8"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="19"/>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="21"/>
       <c r="B39" s="2" t="s">
         <v>6</v>
       </c>
@@ -3248,64 +3298,64 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="27"/>
-      <c r="B40" s="28" t="s">
+    <row r="40" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="22"/>
+      <c r="B40" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="C40" s="29"/>
-      <c r="D40" s="30"/>
-    </row>
-    <row r="41" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="18" t="s">
+      <c r="C40" s="18"/>
+      <c r="D40" s="19"/>
+    </row>
+    <row r="41" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="B41" s="20" t="s">
+      <c r="B41" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="C41" s="21"/>
+      <c r="C41" s="24"/>
       <c r="D41" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="19"/>
-      <c r="B42" s="22" t="s">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="21"/>
+      <c r="B42" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="C42" s="23"/>
+      <c r="C42" s="26"/>
       <c r="D42" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="19"/>
-      <c r="B43" s="22" t="s">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="21"/>
+      <c r="B43" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="C43" s="23"/>
+      <c r="C43" s="26"/>
       <c r="D43" s="8">
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="19"/>
-      <c r="B44" s="22" t="s">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="21"/>
+      <c r="B44" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="C44" s="23"/>
+      <c r="C44" s="26"/>
       <c r="D44" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="19"/>
-      <c r="B45" s="22"/>
-      <c r="C45" s="23"/>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="21"/>
+      <c r="B45" s="25"/>
+      <c r="C45" s="26"/>
       <c r="D45" s="8"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="19"/>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="21"/>
       <c r="B46" s="2" t="s">
         <v>76</v>
       </c>
@@ -3316,56 +3366,56 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="27"/>
-      <c r="B47" s="28" t="s">
+    <row r="47" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="22"/>
+      <c r="B47" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="C47" s="29"/>
-      <c r="D47" s="30"/>
-    </row>
-    <row r="48" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="18" t="s">
+      <c r="C47" s="18"/>
+      <c r="D47" s="19"/>
+    </row>
+    <row r="48" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="B48" s="20" t="s">
+      <c r="B48" s="23" t="s">
         <v>79</v>
       </c>
-      <c r="C48" s="21"/>
+      <c r="C48" s="24"/>
       <c r="D48" s="7">
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="19"/>
-      <c r="B49" s="22" t="s">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="21"/>
+      <c r="B49" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="C49" s="23"/>
+      <c r="C49" s="26"/>
       <c r="D49" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="19"/>
-      <c r="B50" s="22"/>
-      <c r="C50" s="23"/>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="21"/>
+      <c r="B50" s="25"/>
+      <c r="C50" s="26"/>
       <c r="D50" s="8"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="19"/>
-      <c r="B51" s="22"/>
-      <c r="C51" s="23"/>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="21"/>
+      <c r="B51" s="25"/>
+      <c r="C51" s="26"/>
       <c r="D51" s="8"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A52" s="19"/>
-      <c r="B52" s="22"/>
-      <c r="C52" s="23"/>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="21"/>
+      <c r="B52" s="25"/>
+      <c r="C52" s="26"/>
       <c r="D52" s="8"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="19"/>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="21"/>
       <c r="B53" s="2" t="s">
         <v>76</v>
       </c>
@@ -3376,46 +3426,60 @@
         <v>4</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="27"/>
-      <c r="B54" s="28" t="s">
+    <row r="54" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="22"/>
+      <c r="B54" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="C54" s="29"/>
-      <c r="D54" s="30"/>
-    </row>
-    <row r="55" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="18"/>
-      <c r="B55" s="20"/>
-      <c r="C55" s="21"/>
-      <c r="D55" s="7"/>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="19"/>
-      <c r="B56" s="22"/>
-      <c r="C56" s="23"/>
-      <c r="D56" s="8"/>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="19"/>
-      <c r="B57" s="22"/>
-      <c r="C57" s="23"/>
-      <c r="D57" s="8"/>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A58" s="19"/>
-      <c r="B58" s="22"/>
-      <c r="C58" s="23"/>
+      <c r="C54" s="18"/>
+      <c r="D54" s="19"/>
+    </row>
+    <row r="55" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="B55" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="C55" s="24"/>
+      <c r="D55" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="21"/>
+      <c r="B56" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="C56" s="26"/>
+      <c r="D56" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="21"/>
+      <c r="B57" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="C57" s="26"/>
+      <c r="D57" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="21"/>
+      <c r="B58" s="25"/>
+      <c r="C58" s="26"/>
       <c r="D58" s="8"/>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A59" s="19"/>
-      <c r="B59" s="22"/>
-      <c r="C59" s="23"/>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="21"/>
+      <c r="B59" s="25"/>
+      <c r="C59" s="26"/>
       <c r="D59" s="8"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" s="19"/>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="21"/>
       <c r="B60" s="2" t="s">
         <v>6</v>
       </c>
@@ -3424,47 +3488,49 @@
       </c>
       <c r="D60" s="9">
         <f>SUM(D55:D59)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="27"/>
-      <c r="B61" s="28"/>
-      <c r="C61" s="29"/>
-      <c r="D61" s="30"/>
-    </row>
-    <row r="62" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="18"/>
-      <c r="B62" s="20"/>
-      <c r="C62" s="21"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="22"/>
+      <c r="B61" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="C61" s="18"/>
+      <c r="D61" s="19"/>
+    </row>
+    <row r="62" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="20"/>
+      <c r="B62" s="23"/>
+      <c r="C62" s="24"/>
       <c r="D62" s="7"/>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A63" s="19"/>
-      <c r="B63" s="22"/>
-      <c r="C63" s="23"/>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="21"/>
+      <c r="B63" s="25"/>
+      <c r="C63" s="26"/>
       <c r="D63" s="8"/>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A64" s="19"/>
-      <c r="B64" s="22"/>
-      <c r="C64" s="23"/>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="21"/>
+      <c r="B64" s="25"/>
+      <c r="C64" s="26"/>
       <c r="D64" s="8"/>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A65" s="19"/>
-      <c r="B65" s="22"/>
-      <c r="C65" s="23"/>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="21"/>
+      <c r="B65" s="25"/>
+      <c r="C65" s="26"/>
       <c r="D65" s="8"/>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A66" s="19"/>
-      <c r="B66" s="22"/>
-      <c r="C66" s="23"/>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="21"/>
+      <c r="B66" s="25"/>
+      <c r="C66" s="26"/>
       <c r="D66" s="8"/>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A67" s="19"/>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="21"/>
       <c r="B67" s="2" t="s">
         <v>6</v>
       </c>
@@ -3476,44 +3542,44 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="19"/>
-      <c r="B68" s="24"/>
-      <c r="C68" s="25"/>
-      <c r="D68" s="26"/>
-    </row>
-    <row r="69" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="18"/>
-      <c r="B69" s="20"/>
-      <c r="C69" s="21"/>
+    <row r="68" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="21"/>
+      <c r="B68" s="27"/>
+      <c r="C68" s="28"/>
+      <c r="D68" s="29"/>
+    </row>
+    <row r="69" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="20"/>
+      <c r="B69" s="23"/>
+      <c r="C69" s="24"/>
       <c r="D69" s="7"/>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A70" s="19"/>
-      <c r="B70" s="22"/>
-      <c r="C70" s="23"/>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="21"/>
+      <c r="B70" s="25"/>
+      <c r="C70" s="26"/>
       <c r="D70" s="8"/>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A71" s="19"/>
-      <c r="B71" s="22"/>
-      <c r="C71" s="23"/>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="21"/>
+      <c r="B71" s="25"/>
+      <c r="C71" s="26"/>
       <c r="D71" s="8"/>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A72" s="19"/>
-      <c r="B72" s="22"/>
-      <c r="C72" s="23"/>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="21"/>
+      <c r="B72" s="25"/>
+      <c r="C72" s="26"/>
       <c r="D72" s="8"/>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A73" s="19"/>
-      <c r="B73" s="22"/>
-      <c r="C73" s="23"/>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="21"/>
+      <c r="B73" s="25"/>
+      <c r="C73" s="26"/>
       <c r="D73" s="8"/>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A74" s="19"/>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="21"/>
       <c r="B74" s="2" t="s">
         <v>6</v>
       </c>
@@ -3525,44 +3591,44 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="27"/>
-      <c r="B75" s="28"/>
-      <c r="C75" s="29"/>
-      <c r="D75" s="30"/>
-    </row>
-    <row r="76" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="18"/>
-      <c r="B76" s="20"/>
-      <c r="C76" s="21"/>
+    <row r="75" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="22"/>
+      <c r="B75" s="17"/>
+      <c r="C75" s="18"/>
+      <c r="D75" s="19"/>
+    </row>
+    <row r="76" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="20"/>
+      <c r="B76" s="23"/>
+      <c r="C76" s="24"/>
       <c r="D76" s="7"/>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A77" s="19"/>
-      <c r="B77" s="22"/>
-      <c r="C77" s="23"/>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="21"/>
+      <c r="B77" s="25"/>
+      <c r="C77" s="26"/>
       <c r="D77" s="8"/>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A78" s="19"/>
-      <c r="B78" s="22"/>
-      <c r="C78" s="23"/>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="21"/>
+      <c r="B78" s="25"/>
+      <c r="C78" s="26"/>
       <c r="D78" s="8"/>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A79" s="19"/>
-      <c r="B79" s="22"/>
-      <c r="C79" s="23"/>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="21"/>
+      <c r="B79" s="25"/>
+      <c r="C79" s="26"/>
       <c r="D79" s="8"/>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A80" s="19"/>
-      <c r="B80" s="22"/>
-      <c r="C80" s="23"/>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="21"/>
+      <c r="B80" s="25"/>
+      <c r="C80" s="26"/>
       <c r="D80" s="8"/>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A81" s="19"/>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="21"/>
       <c r="B81" s="2" t="s">
         <v>6</v>
       </c>
@@ -3574,13 +3640,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="27"/>
-      <c r="B82" s="28"/>
-      <c r="C82" s="29"/>
-      <c r="D82" s="30"/>
-    </row>
-    <row r="83" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="22"/>
+      <c r="B82" s="17"/>
+      <c r="C82" s="18"/>
+      <c r="D82" s="19"/>
+    </row>
+    <row r="83" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="11"/>
       <c r="B83" s="10"/>
       <c r="C83" s="3" t="s">
@@ -3588,19 +3654,90 @@
       </c>
       <c r="D83" s="12">
         <f>D11+D18+D25+D32+D39+D46+D53+D60+D67+D74+D81</f>
-        <v>38</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A84" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="B84" s="17"/>
-      <c r="C84" s="17"/>
-      <c r="D84" s="17"/>
+      <c r="B84" s="40"/>
+      <c r="C84" s="40"/>
+      <c r="D84" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="81">
+    <mergeCell ref="A84:D84"/>
+    <mergeCell ref="A76:A82"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="A69:A75"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B75:D75"/>
+    <mergeCell ref="A62:A68"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="A55:A61"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="A48:A54"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="A41:A47"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="A34:A40"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="A27:A33"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="A20:A26"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="A13:A19"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A4:A5"/>
@@ -3611,171 +3748,100 @@
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B12:D12"/>
-    <mergeCell ref="A13:A19"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A20:A26"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="A27:A33"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="A34:A40"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="A41:A47"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="A48:A54"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="A55:A61"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="A62:A68"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="A69:A75"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B75:D75"/>
-    <mergeCell ref="A84:D84"/>
-    <mergeCell ref="A76:A82"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B82:D82"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D11">
-    <cfRule type="containsText" dxfId="51" priority="23" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="47" priority="23" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="50" priority="24" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="46" priority="24" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D13:D18">
-    <cfRule type="containsText" dxfId="49" priority="21" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="45" priority="21" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D13)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="48" priority="22" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="44" priority="22" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D13)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D20:D25">
-    <cfRule type="containsText" dxfId="47" priority="3" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="43" priority="3" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D20)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="46" priority="4" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="42" priority="4" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D20)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D27:D32">
-    <cfRule type="containsText" dxfId="45" priority="19" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="41" priority="19" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D27)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="44" priority="20" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="40" priority="20" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D27)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D34:D39">
-    <cfRule type="containsText" dxfId="43" priority="17" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="39" priority="17" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D34)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="42" priority="18" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="38" priority="18" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D34)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D41:D46">
-    <cfRule type="containsText" dxfId="41" priority="9" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="37" priority="9" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D41)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="40" priority="10" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="36" priority="10" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D41)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D48:D53">
-    <cfRule type="containsText" dxfId="39" priority="7" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="35" priority="7" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D48)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="38" priority="8" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="34" priority="8" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D48)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D55:D60">
-    <cfRule type="containsText" dxfId="37" priority="5" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="33" priority="5" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D55)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="36" priority="6" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="32" priority="6" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D55)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D62:D67">
-    <cfRule type="containsText" dxfId="35" priority="15" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="31" priority="15" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D62)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="34" priority="16" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="30" priority="16" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D62)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D69:D74">
-    <cfRule type="containsText" dxfId="33" priority="13" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="29" priority="13" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D69)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="32" priority="14" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="28" priority="14" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D69)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D76:D81">
-    <cfRule type="containsText" dxfId="31" priority="11" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="27" priority="11" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D76)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="30" priority="12" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="26" priority="12" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D76)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D83">
-    <cfRule type="containsText" dxfId="29" priority="1" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="25" priority="1" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D83)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="28" priority="2" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="24" priority="2" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D83)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3798,16 +3864,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48EAF0F3-3EF4-4217-9640-9C9A8BC6D0F3}">
   <dimension ref="A1:D84"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.54296875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" style="1"/>
-    <col min="2" max="3" width="31.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" style="1" customWidth="1"/>
-    <col min="5" max="217" width="9.140625" style="1" customWidth="1"/>
-    <col min="218" max="16384" width="11.5703125" style="1"/>
+    <col min="1" max="1" width="11.54296875" style="1"/>
+    <col min="2" max="3" width="31.7265625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.7265625" style="1" customWidth="1"/>
+    <col min="5" max="217" width="9.1796875" style="1" customWidth="1"/>
+    <col min="218" max="16384" width="11.54296875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="20" x14ac:dyDescent="0.4">
       <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
@@ -3815,7 +3881,7 @@
       <c r="C1" s="31"/>
       <c r="D1" s="31"/>
     </row>
-    <row r="2" spans="1:4" ht="18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A2" s="38" t="s">
         <v>31</v>
       </c>
@@ -3825,7 +3891,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="32" t="s">
         <v>2</v>
       </c>
@@ -3837,7 +3903,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="34"/>
       <c r="B5" s="34"/>
       <c r="C5" s="35"/>
@@ -3845,8 +3911,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="40">
+    <row r="6" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="30">
         <v>45992</v>
       </c>
       <c r="B6" s="36" t="s">
@@ -3857,34 +3923,34 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="19"/>
-      <c r="B7" s="22" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="21"/>
+      <c r="B7" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="23"/>
+      <c r="C7" s="26"/>
       <c r="D7" s="8">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="19"/>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="21"/>
       <c r="D8" s="8"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="19"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="23"/>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="21"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="26"/>
       <c r="D9" s="8"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="19"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="23"/>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="21"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="26"/>
       <c r="D10" s="8"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="19"/>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="21"/>
       <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
@@ -3896,54 +3962,54 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="19"/>
-      <c r="B12" s="24"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="26"/>
-    </row>
-    <row r="13" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="18">
+    <row r="12" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="21"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="29"/>
+    </row>
+    <row r="13" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="20">
         <v>45993</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="21"/>
+      <c r="C13" s="24"/>
       <c r="D13" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="19"/>
-      <c r="B14" s="22" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="21"/>
+      <c r="B14" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="23"/>
+      <c r="C14" s="26"/>
       <c r="D14" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="19"/>
-      <c r="B15" s="22"/>
-      <c r="C15" s="23"/>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="21"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="26"/>
       <c r="D15" s="8"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="19"/>
-      <c r="B16" s="22"/>
-      <c r="C16" s="23"/>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="21"/>
+      <c r="B16" s="25"/>
+      <c r="C16" s="26"/>
       <c r="D16" s="8"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="19"/>
-      <c r="B17" s="22"/>
-      <c r="C17" s="23"/>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="21"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="26"/>
       <c r="D17" s="8"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="19"/>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="21"/>
       <c r="B18" s="2" t="s">
         <v>6</v>
       </c>
@@ -3955,66 +4021,66 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="19"/>
-      <c r="B19" s="24"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="26"/>
-    </row>
-    <row r="20" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="18">
+    <row r="19" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="21"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="29"/>
+    </row>
+    <row r="20" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="20">
         <v>46000</v>
       </c>
-      <c r="B20" s="20" t="s">
+      <c r="B20" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="21"/>
+      <c r="C20" s="24"/>
       <c r="D20" s="7">
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="19"/>
-      <c r="B21" s="22" t="s">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="21"/>
+      <c r="B21" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="23"/>
+      <c r="C21" s="26"/>
       <c r="D21" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="19"/>
-      <c r="B22" s="22" t="s">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="21"/>
+      <c r="B22" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="23"/>
+      <c r="C22" s="26"/>
       <c r="D22" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="19"/>
-      <c r="B23" s="22" t="s">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="21"/>
+      <c r="B23" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="23"/>
+      <c r="C23" s="26"/>
       <c r="D23" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="19"/>
-      <c r="B24" s="22" t="s">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="21"/>
+      <c r="B24" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="23"/>
+      <c r="C24" s="26"/>
       <c r="D24" s="8">
         <v>0.8</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="19"/>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="21"/>
       <c r="B25" s="2" t="s">
         <v>6</v>
       </c>
@@ -4026,66 +4092,66 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="19"/>
-      <c r="B26" s="24"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="26"/>
-    </row>
-    <row r="27" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="18">
+    <row r="26" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="21"/>
+      <c r="B26" s="27"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="29"/>
+    </row>
+    <row r="27" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="20">
         <v>46006</v>
       </c>
-      <c r="B27" s="20" t="s">
+      <c r="B27" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="21"/>
+      <c r="C27" s="24"/>
       <c r="D27" s="7">
         <v>0.2</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="19"/>
-      <c r="B28" s="22" t="s">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="21"/>
+      <c r="B28" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="23"/>
+      <c r="C28" s="26"/>
       <c r="D28" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="19"/>
-      <c r="B29" s="22" t="s">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="21"/>
+      <c r="B29" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="C29" s="23"/>
+      <c r="C29" s="26"/>
       <c r="D29" s="8">
         <v>1.5</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="19"/>
-      <c r="B30" s="22" t="s">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="21"/>
+      <c r="B30" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="C30" s="23"/>
+      <c r="C30" s="26"/>
       <c r="D30" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="19"/>
-      <c r="B31" s="22" t="s">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="21"/>
+      <c r="B31" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="C31" s="23"/>
+      <c r="C31" s="26"/>
       <c r="D31" s="8">
         <v>0.3</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="19"/>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="21"/>
       <c r="B32" s="2" t="s">
         <v>6</v>
       </c>
@@ -4097,60 +4163,60 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="19"/>
-      <c r="B33" s="24" t="s">
+    <row r="33" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="21"/>
+      <c r="B33" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="C33" s="25"/>
-      <c r="D33" s="26"/>
-    </row>
-    <row r="34" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="18">
+      <c r="C33" s="28"/>
+      <c r="D33" s="29"/>
+    </row>
+    <row r="34" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="20">
         <v>46007</v>
       </c>
-      <c r="B34" s="20" t="s">
+      <c r="B34" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="C34" s="21"/>
+      <c r="C34" s="24"/>
       <c r="D34" s="7">
         <v>0.8</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="19"/>
-      <c r="B35" s="22" t="s">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="21"/>
+      <c r="B35" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="C35" s="23"/>
+      <c r="C35" s="26"/>
       <c r="D35" s="8">
         <v>2.5</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="19"/>
-      <c r="B36" s="22" t="s">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="21"/>
+      <c r="B36" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="23"/>
+      <c r="C36" s="26"/>
       <c r="D36" s="8">
         <v>0.7</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="19"/>
-      <c r="B37" s="22"/>
-      <c r="C37" s="23"/>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="21"/>
+      <c r="B37" s="25"/>
+      <c r="C37" s="26"/>
       <c r="D37" s="8"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="19"/>
-      <c r="B38" s="22"/>
-      <c r="C38" s="23"/>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="21"/>
+      <c r="B38" s="25"/>
+      <c r="C38" s="26"/>
       <c r="D38" s="8"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="19"/>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="21"/>
       <c r="B39" s="2" t="s">
         <v>6</v>
       </c>
@@ -4162,60 +4228,60 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="19"/>
-      <c r="B40" s="24" t="s">
+    <row r="40" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="21"/>
+      <c r="B40" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="C40" s="25"/>
-      <c r="D40" s="26"/>
-    </row>
-    <row r="41" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="18">
+      <c r="C40" s="28"/>
+      <c r="D40" s="29"/>
+    </row>
+    <row r="41" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="20">
         <v>46027</v>
       </c>
-      <c r="B41" s="20" t="s">
+      <c r="B41" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="C41" s="21"/>
+      <c r="C41" s="24"/>
       <c r="D41" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="19"/>
-      <c r="B42" s="22" t="s">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="21"/>
+      <c r="B42" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="C42" s="23"/>
+      <c r="C42" s="26"/>
       <c r="D42" s="8">
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="19"/>
-      <c r="B43" s="22" t="s">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="21"/>
+      <c r="B43" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="C43" s="23"/>
+      <c r="C43" s="26"/>
       <c r="D43" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="19"/>
-      <c r="B44" s="22"/>
-      <c r="C44" s="23"/>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="21"/>
+      <c r="B44" s="25"/>
+      <c r="C44" s="26"/>
       <c r="D44" s="8"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="19"/>
-      <c r="B45" s="22"/>
-      <c r="C45" s="23"/>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="21"/>
+      <c r="B45" s="25"/>
+      <c r="C45" s="26"/>
       <c r="D45" s="8"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="19"/>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="21"/>
       <c r="B46" s="2" t="s">
         <v>6</v>
       </c>
@@ -4227,54 +4293,54 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="27"/>
-      <c r="B47" s="28"/>
-      <c r="C47" s="29"/>
-      <c r="D47" s="30"/>
-    </row>
-    <row r="48" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="18">
+    <row r="47" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="22"/>
+      <c r="B47" s="17"/>
+      <c r="C47" s="18"/>
+      <c r="D47" s="19"/>
+    </row>
+    <row r="48" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="20">
         <v>46028</v>
       </c>
-      <c r="B48" s="20" t="s">
+      <c r="B48" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="C48" s="21"/>
+      <c r="C48" s="24"/>
       <c r="D48" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="19"/>
-      <c r="B49" s="22" t="s">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="21"/>
+      <c r="B49" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="C49" s="23"/>
+      <c r="C49" s="26"/>
       <c r="D49" s="8">
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="19"/>
-      <c r="B50" s="22"/>
-      <c r="C50" s="23"/>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="21"/>
+      <c r="B50" s="25"/>
+      <c r="C50" s="26"/>
       <c r="D50" s="8"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="19"/>
-      <c r="B51" s="22"/>
-      <c r="C51" s="23"/>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="21"/>
+      <c r="B51" s="25"/>
+      <c r="C51" s="26"/>
       <c r="D51" s="8"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A52" s="19"/>
-      <c r="B52" s="22"/>
-      <c r="C52" s="23"/>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="21"/>
+      <c r="B52" s="25"/>
+      <c r="C52" s="26"/>
       <c r="D52" s="8"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="19"/>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="21"/>
       <c r="B53" s="2" t="s">
         <v>6</v>
       </c>
@@ -4286,46 +4352,60 @@
         <v>4</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="27"/>
-      <c r="B54" s="28" t="s">
+    <row r="54" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="22"/>
+      <c r="B54" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="C54" s="29"/>
-      <c r="D54" s="30"/>
-    </row>
-    <row r="55" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="18"/>
-      <c r="B55" s="20"/>
-      <c r="C55" s="21"/>
-      <c r="D55" s="7"/>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="19"/>
-      <c r="B56" s="22"/>
-      <c r="C56" s="23"/>
-      <c r="D56" s="8"/>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="19"/>
-      <c r="B57" s="22"/>
-      <c r="C57" s="23"/>
-      <c r="D57" s="8"/>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A58" s="19"/>
-      <c r="B58" s="22"/>
-      <c r="C58" s="23"/>
+      <c r="C54" s="18"/>
+      <c r="D54" s="19"/>
+    </row>
+    <row r="55" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="20">
+        <v>46034</v>
+      </c>
+      <c r="B55" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="C55" s="24"/>
+      <c r="D55" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="21"/>
+      <c r="B56" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="C56" s="26"/>
+      <c r="D56" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="21"/>
+      <c r="B57" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="C57" s="26"/>
+      <c r="D57" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="21"/>
+      <c r="B58" s="25"/>
+      <c r="C58" s="26"/>
       <c r="D58" s="8"/>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A59" s="19"/>
-      <c r="B59" s="22"/>
-      <c r="C59" s="23"/>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="21"/>
+      <c r="B59" s="25"/>
+      <c r="C59" s="26"/>
       <c r="D59" s="8"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" s="19"/>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="21"/>
       <c r="B60" s="2" t="s">
         <v>6</v>
       </c>
@@ -4334,47 +4414,49 @@
       </c>
       <c r="D60" s="9">
         <f>SUM(D55:D59)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="27"/>
-      <c r="B61" s="28"/>
-      <c r="C61" s="29"/>
-      <c r="D61" s="30"/>
-    </row>
-    <row r="62" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="18"/>
-      <c r="B62" s="20"/>
-      <c r="C62" s="21"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="22"/>
+      <c r="B61" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="C61" s="18"/>
+      <c r="D61" s="19"/>
+    </row>
+    <row r="62" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="20"/>
+      <c r="B62" s="23"/>
+      <c r="C62" s="24"/>
       <c r="D62" s="7"/>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A63" s="19"/>
-      <c r="B63" s="22"/>
-      <c r="C63" s="23"/>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="21"/>
+      <c r="B63" s="25"/>
+      <c r="C63" s="26"/>
       <c r="D63" s="8"/>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A64" s="19"/>
-      <c r="B64" s="22"/>
-      <c r="C64" s="23"/>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="21"/>
+      <c r="B64" s="25"/>
+      <c r="C64" s="26"/>
       <c r="D64" s="8"/>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A65" s="19"/>
-      <c r="B65" s="22"/>
-      <c r="C65" s="23"/>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="21"/>
+      <c r="B65" s="25"/>
+      <c r="C65" s="26"/>
       <c r="D65" s="8"/>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A66" s="19"/>
-      <c r="B66" s="22"/>
-      <c r="C66" s="23"/>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="21"/>
+      <c r="B66" s="25"/>
+      <c r="C66" s="26"/>
       <c r="D66" s="8"/>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A67" s="19"/>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="21"/>
       <c r="B67" s="2" t="s">
         <v>6</v>
       </c>
@@ -4386,44 +4468,44 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="19"/>
-      <c r="B68" s="24"/>
-      <c r="C68" s="25"/>
-      <c r="D68" s="26"/>
-    </row>
-    <row r="69" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="18"/>
-      <c r="B69" s="20"/>
-      <c r="C69" s="21"/>
+    <row r="68" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="21"/>
+      <c r="B68" s="27"/>
+      <c r="C68" s="28"/>
+      <c r="D68" s="29"/>
+    </row>
+    <row r="69" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="20"/>
+      <c r="B69" s="23"/>
+      <c r="C69" s="24"/>
       <c r="D69" s="7"/>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A70" s="19"/>
-      <c r="B70" s="22"/>
-      <c r="C70" s="23"/>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="21"/>
+      <c r="B70" s="25"/>
+      <c r="C70" s="26"/>
       <c r="D70" s="8"/>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A71" s="19"/>
-      <c r="B71" s="22"/>
-      <c r="C71" s="23"/>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="21"/>
+      <c r="B71" s="25"/>
+      <c r="C71" s="26"/>
       <c r="D71" s="8"/>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A72" s="19"/>
-      <c r="B72" s="22"/>
-      <c r="C72" s="23"/>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="21"/>
+      <c r="B72" s="25"/>
+      <c r="C72" s="26"/>
       <c r="D72" s="8"/>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A73" s="19"/>
-      <c r="B73" s="22"/>
-      <c r="C73" s="23"/>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="21"/>
+      <c r="B73" s="25"/>
+      <c r="C73" s="26"/>
       <c r="D73" s="8"/>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A74" s="19"/>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="21"/>
       <c r="B74" s="2" t="s">
         <v>6</v>
       </c>
@@ -4435,44 +4517,44 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="27"/>
-      <c r="B75" s="28"/>
-      <c r="C75" s="29"/>
-      <c r="D75" s="30"/>
-    </row>
-    <row r="76" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="18"/>
-      <c r="B76" s="20"/>
-      <c r="C76" s="21"/>
+    <row r="75" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="22"/>
+      <c r="B75" s="17"/>
+      <c r="C75" s="18"/>
+      <c r="D75" s="19"/>
+    </row>
+    <row r="76" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="20"/>
+      <c r="B76" s="23"/>
+      <c r="C76" s="24"/>
       <c r="D76" s="7"/>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A77" s="19"/>
-      <c r="B77" s="22"/>
-      <c r="C77" s="23"/>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="21"/>
+      <c r="B77" s="25"/>
+      <c r="C77" s="26"/>
       <c r="D77" s="8"/>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A78" s="19"/>
-      <c r="B78" s="22"/>
-      <c r="C78" s="23"/>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="21"/>
+      <c r="B78" s="25"/>
+      <c r="C78" s="26"/>
       <c r="D78" s="8"/>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A79" s="19"/>
-      <c r="B79" s="22"/>
-      <c r="C79" s="23"/>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="21"/>
+      <c r="B79" s="25"/>
+      <c r="C79" s="26"/>
       <c r="D79" s="8"/>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A80" s="19"/>
-      <c r="B80" s="22"/>
-      <c r="C80" s="23"/>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="21"/>
+      <c r="B80" s="25"/>
+      <c r="C80" s="26"/>
       <c r="D80" s="8"/>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A81" s="19"/>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="21"/>
       <c r="B81" s="2" t="s">
         <v>6</v>
       </c>
@@ -4484,13 +4566,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="27"/>
-      <c r="B82" s="28"/>
-      <c r="C82" s="29"/>
-      <c r="D82" s="30"/>
-    </row>
-    <row r="83" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="22"/>
+      <c r="B82" s="17"/>
+      <c r="C82" s="18"/>
+      <c r="D82" s="19"/>
+    </row>
+    <row r="83" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="11"/>
       <c r="B83" s="10"/>
       <c r="C83" s="3" t="s">
@@ -4501,16 +4583,87 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A84" s="17" t="s">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="B84" s="17"/>
-      <c r="C84" s="17"/>
-      <c r="D84" s="17"/>
+      <c r="B84" s="40"/>
+      <c r="C84" s="40"/>
+      <c r="D84" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="81">
+    <mergeCell ref="A84:D84"/>
+    <mergeCell ref="A76:A82"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="A69:A75"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B75:D75"/>
+    <mergeCell ref="A62:A68"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="A55:A61"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="A48:A54"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="A41:A47"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="A34:A40"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="A27:A33"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="A20:A26"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="A13:A19"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A4:A5"/>
@@ -4521,171 +4674,100 @@
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B12:D12"/>
-    <mergeCell ref="A13:A19"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A20:A26"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="A27:A33"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="A34:A40"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="A41:A47"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="A48:A54"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="A55:A61"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="A62:A68"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="A69:A75"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B75:D75"/>
-    <mergeCell ref="A84:D84"/>
-    <mergeCell ref="A76:A82"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B82:D82"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D11">
-    <cfRule type="containsText" dxfId="27" priority="13" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="23" priority="13" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="26" priority="14" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="22" priority="14" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D13:D18">
-    <cfRule type="containsText" dxfId="25" priority="11" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="21" priority="11" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D13)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="12" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="20" priority="12" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D13)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D20:D25">
-    <cfRule type="containsText" dxfId="23" priority="9" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="19" priority="9" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D20)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="22" priority="10" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="18" priority="10" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D20)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D27:D32">
-    <cfRule type="containsText" dxfId="21" priority="7" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="17" priority="7" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D27)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="8" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="16" priority="8" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D27)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D34:D39">
-    <cfRule type="containsText" dxfId="19" priority="5" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="15" priority="5" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D34)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="6" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="14" priority="6" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D34)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D41:D46">
-    <cfRule type="containsText" dxfId="17" priority="3" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="13" priority="3" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D41)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="4" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="12" priority="4" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D41)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D48:D53">
-    <cfRule type="containsText" dxfId="15" priority="1" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="11" priority="1" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D48)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="2" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="10" priority="2" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D48)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D55:D60">
-    <cfRule type="containsText" dxfId="13" priority="19" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="9" priority="19" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D55)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="20" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="8" priority="20" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D55)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D62:D67">
-    <cfRule type="containsText" dxfId="11" priority="29" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="7" priority="29" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D62)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="30" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="6" priority="30" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D62)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D69:D74">
-    <cfRule type="containsText" dxfId="9" priority="27" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="5" priority="27" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D69)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="28" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="4" priority="28" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D69)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D76:D81">
-    <cfRule type="containsText" dxfId="7" priority="25" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="3" priority="25" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D76)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="26" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="2" priority="26" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D76)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D83">
-    <cfRule type="containsText" dxfId="5" priority="15" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="1" priority="15" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D83)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="16" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="0" priority="16" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D83)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4706,6 +4788,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8afaa137-8a18-4908-97f4-35fc924e5a91">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3b60234b-33e6-42ae-ae88-ba7d4a3eedfd" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006BD0882D7B13D249A8B88997E24B9140" ma:contentTypeVersion="14" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="3865b25f2bf2a035dbe7787239b3f11c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8afaa137-8a18-4908-97f4-35fc924e5a91" xmlns:ns3="3b60234b-33e6-42ae-ae88-ba7d4a3eedfd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="718f9f7ddd2530d56a17ab9424d0abda" ns2:_="" ns3:_="">
     <xsd:import namespace="8afaa137-8a18-4908-97f4-35fc924e5a91"/>
@@ -4918,27 +5020,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1CED954-0C0B-4246-88BC-C0C5C061E08E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="3b60234b-33e6-42ae-ae88-ba7d4a3eedfd"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="8afaa137-8a18-4908-97f4-35fc924e5a91"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8afaa137-8a18-4908-97f4-35fc924e5a91">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3b60234b-33e6-42ae-ae88-ba7d4a3eedfd" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8C0AFF7-6D45-4588-A3CE-0506D82134A8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84AEF82B-2BAE-481D-A319-B09ADD6915E9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4955,29 +5062,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8C0AFF7-6D45-4588-A3CE-0506D82134A8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1CED954-0C0B-4246-88BC-C0C5C061E08E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="3b60234b-33e6-42ae-ae88-ba7d4a3eedfd"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="8afaa137-8a18-4908-97f4-35fc924e5a91"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>